--- a/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
+++ b/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
@@ -434,16 +434,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CookingTables 填写说明（对齐 ScriptableObject 文档）</t>
+          <t>七日食谱表（CookingTables）</t>
         </is>
       </c>
     </row>
@@ -453,168 +453,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>导入菜单：Cooking / Import Cooking Tables</t>
+          <t>导入：Cooking / Import Cooking Tables</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>数据 Sheet 第一行必须是英文表头；不要在表头上方插说明行。</t>
+          <t>第一行必须是英文表头。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>shape：Whole/Dice/Slice/Shred；cookMethod：Raw/Boiled/Fried/BoiledAndFried</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【Seasonings】调味料 → Data/Seasonings/</t>
+          <t>RecipeSeasonings 行序 = 该食材上调料顺序。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  id：建好不要改，如 season_salt</t>
+          <t>RecipeSteps 为日记文案；暂可不参与判定。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  displayName：界面显示名，如 盐</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  icon：图标路径，可空</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>【Recipes】食谱头信息 → Data/Recipes/（一份资产一道菜）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  id / displayName / unlockDay / finishedSprite（可空）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  第7天火锅：RecipeIngredients 与 RecipeSeasonings 可不写该 recipeId</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>【RecipeIngredients】成菜要求</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  recipeId, ingredientId, shape, cookMethod, count</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  shape：Whole / Dice / Slice / Shred</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  cookMethod：Raw / Boiled / Fried / BoiledAndFried</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  count 空或≤0 时按 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>【RecipeSeasonings】调味顺序（行序=玩家必须倒的顺序）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  recipeId, seasoningId, targetIngredientId, count</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>【RecipeSteps】日记步骤——功能未接入，暂时不用写</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  action：Cut / Boil / Fry / Season / Plate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>【Ingredients】原食材 → Data/Ingredients/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  id 建好不要改；spriteWhole / baseColor 可空（空则保留已有图）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>【IngredientVisualStates】可选，状态图标；不写则保留资产现有列表</t>
+          <t>DAY7 火锅：ingredients/seasonings 留空。</t>
         </is>
       </c>
     </row>
@@ -629,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -688,10 +562,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>胡椒</t>
+          <t>黑胡椒</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>season_sugar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>糖</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>season_sauce</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>酱料</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>season_spice</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>香料</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -704,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -750,6 +663,102 @@
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>recipe_day2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>虹彩北非蛋</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>蜜莓酱香煎玉米鱼</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>recipe_day4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>幽灵布丁船</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>海鲜杂烩饭</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>鸟巢山药饼</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>recipe_day7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>七日火锅</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -762,7 +771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -827,22 +836,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>recipe_day1</t>
+          <t>recipe_day2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ing_onion</t>
+          <t>ing_beef</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Slice</t>
+          <t>Dice</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BoiledAndFried</t>
+          <t>Fried</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -852,25 +861,400 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>recipe_day1</t>
+          <t>recipe_day2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ing_potato</t>
+          <t>ing_onion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>recipe_day2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ing_tomato</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>recipe_day2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ing_egg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ing_berry</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>recipe_day4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ing_pumpkin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>recipe_day4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ing_berry</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ing_onion</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ing_tomato</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ing_rice</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ing_shrimp</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ing_yam</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Shred</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ing_doneegg</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ing_tomato</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dice</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ing_cucumber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Slice</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Boiled</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -885,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -959,17 +1343,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>recipe_day1</t>
+          <t>recipe_day2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>season_pepper</t>
+          <t>season_oil</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ing_mushroom</t>
+          <t>ing_onion</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -979,12 +1363,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recipe_day1</t>
+          <t>recipe_day2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>season_oil</t>
+          <t>season_salt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -999,17 +1383,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>recipe_day1</t>
+          <t>recipe_day2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>season_salt</t>
+          <t>season_oil</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ing_onion</t>
+          <t>ing_beef</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1019,17 +1403,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>recipe_day1</t>
+          <t>recipe_day2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>season_pepper</t>
+          <t>season_salt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ing_onion</t>
+          <t>ing_beef</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1039,17 +1423,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>recipe_day1</t>
+          <t>recipe_day2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>season_salt</t>
+          <t>season_pepper</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ing_potato</t>
+          <t>ing_egg</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1059,20 +1443,420 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>recipe_day1</t>
+          <t>recipe_day2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>season_spice</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ing_egg</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>season_sugar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ing_berry</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>season_salt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>season_pepper</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ing_potato</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>recipe_day4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>season_sugar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ing_pumpkin</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>recipe_day4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>season_sauce</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ing_pumpkin</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ing_onion</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ing_tomato</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>season_salt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ing_rice</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>season_pepper</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>season_pepper</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ing_shrimp</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>season_salt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ing_yam</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>season_pepper</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ing_yam</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ing_yam</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>season_sauce</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ing_doneegg</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>season_sauce</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ing_tomato</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>season_sauce</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ing_cucumber</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>season_pepper</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ing_doneegg</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>season_pepper</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ing_tomato</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>season_pepper</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ing_cucumber</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1087,16 +1871,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,6 +1919,798 @@
           <t>seasoningId</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>recipe_day1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>白蘑菇切片。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ing_mushroom</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>recipe_day1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>锅中放油，加入蘑菇，炒至焦香。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ing_mushroom</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>recipe_day1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>开始炖煮。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ing_mushroom</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BoiledAndFried</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>recipe_day1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>记得使用盐调味。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ing_mushroom</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BoiledAndFried</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>season_salt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>recipe_day2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>牛肉、洋葱、番茄切丁。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ing_beef</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>recipe_day2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>锅中放油，分别加入洋葱和牛肉炒至出水，加盐。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ing_beef</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>recipe_day2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>倒入番茄丁，收浓汤汁。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ing_tomato</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>recipe_day2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>打入鸡蛋焖煮，出锅前加入黑胡椒与香料调味。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ing_egg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>season_pepper</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>玉米鱼切块，蜜莓果切小丁。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>蜜莓果加糖，煮到浓稠。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ing_berry</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>season_sugar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>锅热放油，玉米鱼煎至两面金黄，加入盐和黑胡椒调味。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>recipe_day3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>鱼肉装盘，淋上蜜莓酱。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Plate</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>recipe_day4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>幽灵南瓜切块，煮熟冷却后加入奶油翻拌成泥。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ing_pumpkin</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>recipe_day4</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>在盘子上摆出幽灵的形状，使用巧克力酱画出表情。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ing_pumpkin</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>season_sauce</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>recipe_day4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>在周围放置奶油、蜜莓果、糖果进行装饰。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Plate</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ing_berry</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>鱼切块，处理好虾。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>锅中放油，依次加入洋葱与番茄，炒到出汁成酱。</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ing_onion</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>倒入大米翻炒，加入盐拌匀。</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ing_rice</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>season_salt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>铺上处理好的鱼和虾进行焖煮。</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Boil</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ing_cornfish</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>recipe_day5</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>出锅前可再次进行调味。</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ing_shrimp</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Boiled</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>season_pepper</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>鸡蛋煮熟后切丁，番茄切丁、黄瓜切片，山药切丝。</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ing_yam</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>山药丝加入盐和黑胡椒调味，锅中加油，将山药丝煎成饼。</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ing_yam</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>season_oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>将鸡蛋丁、番茄丁、黄瓜片与沙拉酱、黑胡椒拌匀。</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ing_doneegg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>season_sauce</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>recipe_day6</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>组装：取一张山药饼固定成碗状，中间放上拌好的沙拉。</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Plate</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ing_yam</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fried</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
+++ b/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
@@ -983,15 +983,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -1004,8 +1005,18 @@
       <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>pageSpriteZh</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>pageSpriteEn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1015,8 +1026,13 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1026,8 +1042,13 @@
       <c r="C3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1038,7 +1059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1049,7 +1070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1059,8 +1080,13 @@
       <c r="C6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day5.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1071,7 +1097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>

--- a/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
+++ b/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\TGJ_music\CookingClient\Assets\_Project\Data\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB448C1-DB81-461D-8AB9-849658B21E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6B9BEF-2784-47EA-90CA-20CB3F3D31E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12610" windowHeight="15370" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="169">
   <si>
     <t>七日食谱表（CookingTables）</t>
   </si>
@@ -396,9 +396,6 @@
   </si>
   <si>
     <t>生长在森林中的菌类，形似夜空中皎白的明月。</t>
-  </si>
-  <si>
-    <t>Assets/_Project/Arts/AI/Mushroom.png</t>
   </si>
   <si>
     <t>洋葱</t>
@@ -493,6 +490,73 @@
   </si>
   <si>
     <t>ing_berry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pageSpriteZh</t>
+  </si>
+  <si>
+    <t>pageSpriteEn</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day1.png</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day2.png</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day5.png</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day3.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day4.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day6.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Mushroom_b.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Beef.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Berry.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Yam.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Tomato.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Shrimp_Sliced.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Rice01.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Pumpkin.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Onion.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Egg.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1005,15 +1069,11 @@
       <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>pageSpriteZh</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>pageSpriteEn</t>
-        </is>
+      <c r="E1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1026,10 +1086,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day1.png</t>
-        </is>
+      <c r="E2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1042,10 +1100,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day2.png</t>
-        </is>
+      <c r="E3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1058,6 +1114,9 @@
       <c r="C4">
         <v>3</v>
       </c>
+      <c r="E4" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1069,6 +1128,9 @@
       <c r="C5">
         <v>4</v>
       </c>
+      <c r="E5" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1080,10 +1142,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Assets/_Project/Arts/UI/Recipe/Recipe_Day5.png</t>
-        </is>
+      <c r="E6" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1095,6 +1155,9 @@
       </c>
       <c r="C7">
         <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1216,7 +1279,7 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>52</v>
@@ -1307,7 +1370,7 @@
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1324,7 +1387,7 @@
         <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1341,7 +1404,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1409,7 +1472,7 @@
         <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1572,7 +1635,7 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1586,7 +1649,7 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1678,13 +1741,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" t="s">
         <v>149</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>150</v>
-      </c>
-      <c r="C16" t="s">
-        <v>151</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1706,13 +1769,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" t="s">
         <v>144</v>
       </c>
-      <c r="B18" t="s">
-        <v>145</v>
-      </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1734,13 +1797,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" t="s">
         <v>144</v>
       </c>
-      <c r="B20" t="s">
-        <v>145</v>
-      </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1762,13 +1825,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" t="s">
         <v>144</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>145</v>
-      </c>
-      <c r="C22" t="s">
-        <v>146</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2565,6 +2628,9 @@
       <c r="H2">
         <v>160</v>
       </c>
+      <c r="I2" t="s">
+        <v>160</v>
+      </c>
       <c r="J2" t="s">
         <v>109</v>
       </c>
@@ -2594,6 +2660,9 @@
       <c r="H3">
         <v>140</v>
       </c>
+      <c r="I3" t="s">
+        <v>161</v>
+      </c>
       <c r="J3" t="s">
         <v>109</v>
       </c>
@@ -2710,6 +2779,9 @@
       <c r="H7">
         <v>170</v>
       </c>
+      <c r="I7" t="s">
+        <v>168</v>
+      </c>
       <c r="J7" t="s">
         <v>109</v>
       </c>
@@ -2740,7 +2812,7 @@
         <v>180</v>
       </c>
       <c r="I8" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="J8" t="s">
         <v>109</v>
@@ -2751,10 +2823,10 @@
         <v>49</v>
       </c>
       <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" t="s">
         <v>124</v>
-      </c>
-      <c r="C9" t="s">
-        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>112</v>
@@ -2771,19 +2843,22 @@
       <c r="H9">
         <v>170</v>
       </c>
+      <c r="I9" t="s">
+        <v>167</v>
+      </c>
       <c r="J9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s">
         <v>126</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>127</v>
-      </c>
-      <c r="C10" t="s">
-        <v>128</v>
       </c>
       <c r="D10" t="s">
         <v>112</v>
@@ -2809,10 +2884,10 @@
         <v>56</v>
       </c>
       <c r="B11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" t="s">
         <v>129</v>
-      </c>
-      <c r="C11" t="s">
-        <v>130</v>
       </c>
       <c r="D11" t="s">
         <v>112</v>
@@ -2828,6 +2903,9 @@
       </c>
       <c r="H11">
         <v>185</v>
+      </c>
+      <c r="I11" t="s">
+        <v>166</v>
       </c>
       <c r="J11" t="s">
         <v>109</v>
@@ -2838,13 +2916,13 @@
         <v>58</v>
       </c>
       <c r="B12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" t="s">
         <v>131</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>132</v>
-      </c>
-      <c r="D12" t="s">
-        <v>133</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -2857,6 +2935,9 @@
       </c>
       <c r="H12">
         <v>200</v>
+      </c>
+      <c r="I12" t="s">
+        <v>165</v>
       </c>
       <c r="J12" t="s">
         <v>109</v>
@@ -2867,10 +2948,10 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
         <v>134</v>
-      </c>
-      <c r="C13" t="s">
-        <v>135</v>
       </c>
       <c r="D13" t="s">
         <v>108</v>
@@ -2886,6 +2967,9 @@
       </c>
       <c r="H13">
         <v>155</v>
+      </c>
+      <c r="I13" t="s">
+        <v>164</v>
       </c>
       <c r="J13" t="s">
         <v>109</v>
@@ -2896,10 +2980,10 @@
         <v>50</v>
       </c>
       <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
         <v>136</v>
-      </c>
-      <c r="C14" t="s">
-        <v>137</v>
       </c>
       <c r="D14" t="s">
         <v>112</v>
@@ -2915,6 +2999,9 @@
       </c>
       <c r="H14">
         <v>150</v>
+      </c>
+      <c r="I14" t="s">
+        <v>163</v>
       </c>
       <c r="J14" t="s">
         <v>109</v>
@@ -2925,10 +3012,10 @@
         <v>60</v>
       </c>
       <c r="B15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" t="s">
         <v>138</v>
-      </c>
-      <c r="C15" t="s">
-        <v>139</v>
       </c>
       <c r="D15" t="s">
         <v>112</v>
@@ -2944,6 +3031,9 @@
       </c>
       <c r="H15">
         <v>175</v>
+      </c>
+      <c r="I15" t="s">
+        <v>162</v>
       </c>
       <c r="J15" t="s">
         <v>109</v>
@@ -2975,7 +3065,7 @@
         <v>41</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
+++ b/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\TGJ_music\CookingClient\Assets\_Project\Data\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6B9BEF-2784-47EA-90CA-20CB3F3D31E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93716001-76B0-4BD4-BF18-8180BE65AD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12610" windowHeight="15370" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="650" yWindow="1300" windowWidth="18420" windowHeight="13270" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="179">
   <si>
     <t>七日食谱表（CookingTables）</t>
   </si>
@@ -557,6 +557,43 @@
   </si>
   <si>
     <t>Assets/_Project/Arts/Ingrediant/Food_Egg.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Food/Food_Soup.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Food/Food_eggs.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Food/Food_Yampie.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Food/Food_Seafoodrice.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Food/Food_Jellyship.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Food/Food_Friedfish.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Mushroom_Sliced.png</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Mushroom_b.png</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Mushroom_w.png</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/Food_Cucumber.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1052,7 +1089,7 @@
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="49.81640625" customWidth="1"/>
     <col min="5" max="6" width="52" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1086,6 +1123,9 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2" t="s">
+        <v>169</v>
+      </c>
       <c r="E2" t="s">
         <v>153</v>
       </c>
@@ -1100,6 +1140,9 @@
       <c r="C3">
         <v>2</v>
       </c>
+      <c r="D3" t="s">
+        <v>170</v>
+      </c>
       <c r="E3" t="s">
         <v>154</v>
       </c>
@@ -1114,6 +1157,9 @@
       <c r="C4">
         <v>3</v>
       </c>
+      <c r="D4" t="s">
+        <v>174</v>
+      </c>
       <c r="E4" t="s">
         <v>156</v>
       </c>
@@ -1128,6 +1174,9 @@
       <c r="C5">
         <v>4</v>
       </c>
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
       <c r="E5" t="s">
         <v>157</v>
       </c>
@@ -1142,6 +1191,9 @@
       <c r="C6">
         <v>5</v>
       </c>
+      <c r="D6" t="s">
+        <v>172</v>
+      </c>
       <c r="E6" t="s">
         <v>155</v>
       </c>
@@ -1155,6 +1207,9 @@
       </c>
       <c r="C7">
         <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>171</v>
       </c>
       <c r="E7" t="s">
         <v>158</v>
@@ -2721,6 +2776,9 @@
       <c r="H5">
         <v>130</v>
       </c>
+      <c r="I5" t="s">
+        <v>178</v>
+      </c>
       <c r="J5" t="s">
         <v>109</v>
       </c>
@@ -3047,11 +3105,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="4" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="58.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3068,6 +3128,118 @@
         <v>139</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>176</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
+++ b/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\TGJ_music\CookingClient\Assets\_Project\Data\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93716001-76B0-4BD4-BF18-8180BE65AD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF123E3-5FBB-4735-88F5-94952154CBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="650" yWindow="1300" windowWidth="18420" windowHeight="13270" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8400" yWindow="1210" windowWidth="18420" windowHeight="13270" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,15 @@
     <sheet name="RecipeSeasonings" sheetId="5" r:id="rId5"/>
     <sheet name="RecipeSteps" sheetId="6" r:id="rId6"/>
     <sheet name="Ingredients" sheetId="7" r:id="rId7"/>
-    <sheet name="IngredientVisualStates" sheetId="8" r:id="rId8"/>
+    <sheet name="AttributeNames" sheetId="9" r:id="rId8"/>
+    <sheet name="IngredientVisualStates" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="265">
   <si>
     <t>七日食谱表（CookingTables）</t>
   </si>
@@ -594,6 +595,267 @@
   </si>
   <si>
     <t>Assets/_Project/Arts/Ingrediant/Food_Cucumber.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rainbow Beef</t>
+  </si>
+  <si>
+    <t>Beef that shimmers with rainbow colors, where the most delicious essence is concentrated.</t>
+  </si>
+  <si>
+    <t>Honeyberry</t>
+  </si>
+  <si>
+    <t>A sweet fruit. Eat too many at once and you might get a toothache.</t>
+  </si>
+  <si>
+    <t>Cornfish</t>
+  </si>
+  <si>
+    <t>A yellow, scaly fish with sweet, tender flesh. No wonder it's likened to corn.</t>
+  </si>
+  <si>
+    <t>Cucumber</t>
+  </si>
+  <si>
+    <t>A crisp, refreshing gourd that brings a burst of fresh aroma to everyone.</t>
+  </si>
+  <si>
+    <t>Boiled Egg</t>
+  </si>
+  <si>
+    <t>An egg boiled in water, with the white wrapping around a plump yolk. Perfect!</t>
+  </si>
+  <si>
+    <t>Egg</t>
+  </si>
+  <si>
+    <t>An egg laid by some unknown kind of chicken. It looks perfectly ordinary, and hopefully tastes that way too.</t>
+  </si>
+  <si>
+    <t>White Mushroom</t>
+  </si>
+  <si>
+    <t>A fungus that grows in the forest, shaped like a bright white moon in the night sky.</t>
+  </si>
+  <si>
+    <t>Onion</t>
+  </si>
+  <si>
+    <t>A wild onion that grows in the forest, with a pungent yet sweet taste.</t>
+  </si>
+  <si>
+    <t>Star Potato</t>
+  </si>
+  <si>
+    <t>It looks much like an ordinary potato, but the inside shows a star-shaped pattern when it is cut open.</t>
+  </si>
+  <si>
+    <t>Ghost Pumpkin</t>
+  </si>
+  <si>
+    <t>A white pumpkin with face-like patterns. Is it born that way, or is it the lingering will of the dead? No one knows the answer.</t>
+  </si>
+  <si>
+    <t>Rice</t>
+  </si>
+  <si>
+    <t>A grain that looks like rice and tastes pretty close to it too. Might as well just call it rice.</t>
+  </si>
+  <si>
+    <t>Red-Spotted Shrimp</t>
+  </si>
+  <si>
+    <t>A reddish-brown shrimp covered in spots. They say the more spots, the more delicious.</t>
+  </si>
+  <si>
+    <t>Tomato</t>
+  </si>
+  <si>
+    <t>A bright red fruit with a slight sourness that whets the appetite.</t>
+  </si>
+  <si>
+    <t>Yam</t>
+  </si>
+  <si>
+    <t>Looks like a furry tree branch. Some say it's a cousin of the potato, but I don't buy it.</t>
+  </si>
+  <si>
+    <t>textZh</t>
+  </si>
+  <si>
+    <t>textEn</t>
+  </si>
+  <si>
+    <t>label.description</t>
+  </si>
+  <si>
+    <t>食物描述：</t>
+  </si>
+  <si>
+    <t>label.kind</t>
+  </si>
+  <si>
+    <t>类别：</t>
+  </si>
+  <si>
+    <t>Kind:</t>
+  </si>
+  <si>
+    <t>label.optimalDoneness</t>
+  </si>
+  <si>
+    <t>最佳熟度：</t>
+  </si>
+  <si>
+    <t>OptimalDoneness:</t>
+  </si>
+  <si>
+    <t>label.maxDoneness</t>
+  </si>
+  <si>
+    <t>最大熟度：</t>
+  </si>
+  <si>
+    <t>MaxDoneness:</t>
+  </si>
+  <si>
+    <t>label.state</t>
+  </si>
+  <si>
+    <t>状态：</t>
+  </si>
+  <si>
+    <t>State:</t>
+  </si>
+  <si>
+    <t>label.canEatRaw</t>
+  </si>
+  <si>
+    <t>CanEatRaw:</t>
+  </si>
+  <si>
+    <t>label.canCut</t>
+  </si>
+  <si>
+    <t>CanCut:</t>
+  </si>
+  <si>
+    <t>canEatRaw.true</t>
+  </si>
+  <si>
+    <t>可煎煮</t>
+  </si>
+  <si>
+    <t>canEatRaw.false</t>
+  </si>
+  <si>
+    <t>不可煎煮</t>
+  </si>
+  <si>
+    <t>canCut.true</t>
+  </si>
+  <si>
+    <t>可切</t>
+  </si>
+  <si>
+    <t>canCut.false</t>
+  </si>
+  <si>
+    <t>不可切</t>
+  </si>
+  <si>
+    <t>kind.Meat</t>
+  </si>
+  <si>
+    <t>肉类</t>
+  </si>
+  <si>
+    <t>kind.Vegetable</t>
+  </si>
+  <si>
+    <t>蔬菜</t>
+  </si>
+  <si>
+    <t>kind.Other</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>shape.Whole</t>
+  </si>
+  <si>
+    <t>整块</t>
+  </si>
+  <si>
+    <t>shape.Dice</t>
+  </si>
+  <si>
+    <t>切丁状</t>
+  </si>
+  <si>
+    <t>shape.Slice</t>
+  </si>
+  <si>
+    <t>片状</t>
+  </si>
+  <si>
+    <t>shape.Shred</t>
+  </si>
+  <si>
+    <t>丝状</t>
+  </si>
+  <si>
+    <t>cook.Raw</t>
+  </si>
+  <si>
+    <t>生的</t>
+  </si>
+  <si>
+    <t>cook.Boiled</t>
+  </si>
+  <si>
+    <t>煮过</t>
+  </si>
+  <si>
+    <t>cook.Fried</t>
+  </si>
+  <si>
+    <t>煎过</t>
+  </si>
+  <si>
+    <t>cook.BoiledAndFried</t>
+  </si>
+  <si>
+    <t>煎煮过</t>
+  </si>
+  <si>
+    <t>state.joiner</t>
+  </si>
+  <si>
+    <t>；</t>
+  </si>
+  <si>
+    <t>Ingredients 另有 displayNameEn、descriptionEn。英文名为空时界面回退中文。AttributeNames：属性名和固定属性值的中英对照。</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">; </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>displayNameEn</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>descriptionEn</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -601,7 +863,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,6 +889,22 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -654,10 +932,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -960,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -999,6 +1280,11 @@
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -2613,7 +2899,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2624,9 +2910,11 @@
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="38" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="22.453125" customWidth="1"/>
+    <col min="12" max="12" width="135" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -2657,8 +2945,14 @@
       <c r="J1" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -2689,8 +2983,14 @@
       <c r="J2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -2721,8 +3021,14 @@
       <c r="J3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>181</v>
+      </c>
+      <c r="L3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -2750,8 +3056,14 @@
       <c r="J4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>183</v>
+      </c>
+      <c r="L4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -2782,8 +3094,14 @@
       <c r="J5" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>185</v>
+      </c>
+      <c r="L5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -2811,8 +3129,14 @@
       <c r="J6" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>187</v>
+      </c>
+      <c r="L6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -2843,8 +3167,14 @@
       <c r="J7" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>189</v>
+      </c>
+      <c r="L7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2875,8 +3205,14 @@
       <c r="J8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>191</v>
+      </c>
+      <c r="L8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -2907,8 +3243,14 @@
       <c r="J9" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>193</v>
+      </c>
+      <c r="L9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -2936,8 +3278,14 @@
       <c r="J10" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" t="s">
+        <v>195</v>
+      </c>
+      <c r="L10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -2968,8 +3316,14 @@
       <c r="J11" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" t="s">
+        <v>197</v>
+      </c>
+      <c r="L11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -3000,8 +3354,14 @@
       <c r="J12" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" t="s">
+        <v>199</v>
+      </c>
+      <c r="L12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -3032,8 +3392,14 @@
       <c r="J13" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" t="s">
+        <v>201</v>
+      </c>
+      <c r="L13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -3064,8 +3430,14 @@
       <c r="J14" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>203</v>
+      </c>
+      <c r="L14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -3095,6 +3467,12 @@
       </c>
       <c r="J15" t="s">
         <v>109</v>
+      </c>
+      <c r="K15" t="s">
+        <v>205</v>
+      </c>
+      <c r="L15" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -3104,6 +3482,276 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817F8083-EF7C-49A5-9492-A26103C87A7B}">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.36328125" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>243</v>
+      </c>
+      <c r="B17" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B18" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>249</v>
+      </c>
+      <c r="B20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>253</v>
+      </c>
+      <c r="B22" t="s">
+        <v>254</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B23" t="s">
+        <v>256</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" t="s">
+        <v>258</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>

--- a/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
+++ b/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
@@ -5,30 +5,34 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\TGJ_music\CookingClient\Assets\_Project\Data\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\TGJ_music\CookingClient\Assets\_Project\Data\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF123E3-5FBB-4735-88F5-94952154CBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9818EC25-8ABC-4919-A606-567B5A4B8C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8400" yWindow="1210" windowWidth="18420" windowHeight="13270" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1210" windowWidth="18420" windowHeight="13270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
-    <sheet name="Seasonings" sheetId="2" r:id="rId2"/>
-    <sheet name="Recipes" sheetId="3" r:id="rId3"/>
-    <sheet name="RecipeIngredients" sheetId="4" r:id="rId4"/>
-    <sheet name="RecipeSeasonings" sheetId="5" r:id="rId5"/>
-    <sheet name="RecipeSteps" sheetId="6" r:id="rId6"/>
-    <sheet name="Ingredients" sheetId="7" r:id="rId7"/>
-    <sheet name="AttributeNames" sheetId="9" r:id="rId8"/>
-    <sheet name="IngredientVisualStates" sheetId="8" r:id="rId9"/>
+    <sheet name="备忘" sheetId="10" r:id="rId2"/>
+    <sheet name="Seasonings" sheetId="2" r:id="rId3"/>
+    <sheet name="Recipes" sheetId="3" r:id="rId4"/>
+    <sheet name="RecipeIngredients" sheetId="4" r:id="rId5"/>
+    <sheet name="RecipeSeasonings" sheetId="5" r:id="rId6"/>
+    <sheet name="RecipeSteps" sheetId="6" r:id="rId7"/>
+    <sheet name="Ingredients" sheetId="7" r:id="rId8"/>
+    <sheet name="AttributeNames" sheetId="9" r:id="rId9"/>
+    <sheet name="IngredientVisualStates" sheetId="8" r:id="rId10"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">备忘!$A$1:$F$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="496">
   <si>
     <t>七日食谱表（CookingTables）</t>
   </si>
@@ -857,13 +861,706 @@
   <si>
     <t>descriptionEn</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>表</t>
+  </si>
+  <si>
+    <t>列</t>
+  </si>
+  <si>
+    <t>必填</t>
+  </si>
+  <si>
+    <t>含义</t>
+  </si>
+  <si>
+    <t>怎么填</t>
+  </si>
+  <si>
+    <t>例子</t>
+  </si>
+  <si>
+    <t>总则</t>
+  </si>
+  <si>
+    <t>导入</t>
+  </si>
+  <si>
+    <t>必做</t>
+  </si>
+  <si>
+    <t>改表之后游戏不会自己变</t>
+  </si>
+  <si>
+    <t>保存这个 xlsx，回到 Unity，点菜单 Cooking / Import Cooking Tables。控制台没有报错才算导入成功。</t>
+  </si>
+  <si>
+    <t>Cooking / Import Cooking Tables</t>
+  </si>
+  <si>
+    <t>表头</t>
+  </si>
+  <si>
+    <t>必守</t>
+  </si>
+  <si>
+    <t>程序只认第一行的英文列名</t>
+  </si>
+  <si>
+    <t>第一行必须是英文表头。不要在上面再插标题，不要改列名拼写，不要调换后还把列名留下不改。某一列可以换位置，只要表头文字还在。</t>
+  </si>
+  <si>
+    <t>id、displayName</t>
+  </si>
+  <si>
+    <t>一行数据的身份证</t>
+  </si>
+  <si>
+    <t>用小写英文和下划线。食材 ing_ 开头，调味 season_ 开头，食谱 recipe_day1 这种。写进去之后不要改。改了会再生成一份新资产，旧的还留在工程里。同一张表里同一个 id 不要写两行。</t>
+  </si>
+  <si>
+    <t>空行</t>
+  </si>
+  <si>
+    <t>可留</t>
+  </si>
+  <si>
+    <t>id 或主键空着的行</t>
+  </si>
+  <si>
+    <t>整行放空会被跳过，可以当分隔。主键有字、别的必填列空着，导入会报错。</t>
+  </si>
+  <si>
+    <t>删行</t>
+  </si>
+  <si>
+    <t>注意</t>
+  </si>
+  <si>
+    <t>从表里删掉，不会删掉已经导入的资产</t>
+  </si>
+  <si>
+    <t>少了一行，Unity 里原来的食材、调味、食谱文件还在，只打一条保留警告。真要停用，再在工程里处理那份资产。</t>
+  </si>
+  <si>
+    <t>图片</t>
+  </si>
+  <si>
+    <t>看列</t>
+  </si>
+  <si>
+    <t>填 Unity 工程里的资源路径</t>
+  </si>
+  <si>
+    <t>从 Assets/ 写起，用正斜杠。路径必须指向已经导入的图片。格子空着时：成品图、食材整图、调味图标会保留上次的图；食谱页图空着会把页图清掉。</t>
+  </si>
+  <si>
+    <t>枚举</t>
+  </si>
+  <si>
+    <t>只能填规定的英文词</t>
+  </si>
+  <si>
+    <t>不区分大小写，请按备忘里的写法填。填错整行失败，控制台会写出哪一行。</t>
+  </si>
+  <si>
+    <t>Slice、BoiledAndFried</t>
+  </si>
+  <si>
+    <t>布尔</t>
+  </si>
+  <si>
+    <t>是或否</t>
+  </si>
+  <si>
+    <t>填 1 或 0。也可以填 true / false、yes / no。</t>
+  </si>
+  <si>
+    <t>本表</t>
+  </si>
+  <si>
+    <t>不导入</t>
+  </si>
+  <si>
+    <t>备忘和说明只给人看</t>
+  </si>
+  <si>
+    <t>这两张表没有进导入程序。改别的表才要重新导入。</t>
+  </si>
+  <si>
+    <t>Seasonings</t>
+  </si>
+  <si>
+    <t>（这张表）</t>
+  </si>
+  <si>
+    <t>必须有</t>
+  </si>
+  <si>
+    <t>调味料种类</t>
+  </si>
+  <si>
+    <t>一行一种。锅边的瓶子和食谱里的调料都用这里的 id。</t>
+  </si>
+  <si>
+    <t>油、盐、黑胡椒</t>
+  </si>
+  <si>
+    <t>调味料 id</t>
+  </si>
+  <si>
+    <t>season_ 加英文。瓶子、RecipeSeasonings 都填这个。</t>
+  </si>
+  <si>
+    <t>玩家看到的名字</t>
+  </si>
+  <si>
+    <t>现在界面用中文。</t>
+  </si>
+  <si>
+    <t>可空</t>
+  </si>
+  <si>
+    <t>调味瓶图标</t>
+  </si>
+  <si>
+    <t>图片路径。这一列也可以叫 iconPath。空着不会清掉已经导入的图标。</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/....png</t>
+  </si>
+  <si>
+    <t>Recipes</t>
+  </si>
+  <si>
+    <t>一道菜的名字、哪一天、用哪张图</t>
+  </si>
+  <si>
+    <t>食材清单和调料清单不写在这里，写在后面两张表，用同一个 id 对上。</t>
+  </si>
+  <si>
+    <t>食谱 id</t>
+  </si>
+  <si>
+    <t>recipe_day 加天数。评分、食谱页、日记解锁都用它。</t>
+  </si>
+  <si>
+    <t>菜名</t>
+  </si>
+  <si>
+    <t>中文菜名。</t>
+  </si>
+  <si>
+    <t>第几天的菜</t>
+  </si>
+  <si>
+    <t>填数字。空着当成 1。当天 dayIndex 和这个数一样，并且盘子上的做法对得上，才算做对这道菜。</t>
+  </si>
+  <si>
+    <t>做对之后总结界面的成品图</t>
+  </si>
+  <si>
+    <t>图片路径。也可以叫 finishedSpritePath。空着会保留上次导入的成品图，不会清掉。</t>
+  </si>
+  <si>
+    <t>食谱界面的中文页图</t>
+  </si>
+  <si>
+    <t>图片路径。也可以叫 pageSpriteZhPath。空着会把中文页图清掉，食谱页就没有图。</t>
+  </si>
+  <si>
+    <t>食谱界面的英文页图</t>
+  </si>
+  <si>
+    <t>图片路径。也可以叫 pageSpriteEnPath。空着会把英文页图清掉。</t>
+  </si>
+  <si>
+    <t>RecipeIngredients</t>
+  </si>
+  <si>
+    <t>这道菜要哪些食材、切成什么、怎么熟</t>
+  </si>
+  <si>
+    <t>一行是一道菜里的一种食材。同一 recipeId 写多行。火锅这类还没定食材的菜，这里不要写行，清单就是空的。</t>
+  </si>
+  <si>
+    <t>白蘑菇要切片并且煎煮</t>
+  </si>
+  <si>
+    <t>哪道菜</t>
+  </si>
+  <si>
+    <t>必须已经写在 Recipes 的 id 里。</t>
+  </si>
+  <si>
+    <t>哪种食材</t>
+  </si>
+  <si>
+    <t>填 Ingredients 的 id。列表头写成 ingredient Id 也可以。</t>
+  </si>
+  <si>
+    <t>做对时的形状</t>
+  </si>
+  <si>
+    <t>Whole 整块，Dice 切丁，Slice 切片，Shred 切丝。四个词只能填其中一个。</t>
+  </si>
+  <si>
+    <t>做对时的烹饪方法</t>
+  </si>
+  <si>
+    <t>Raw 生的，Boiled 煮过，Fried 煎过，BoiledAndFried 煎煮过（先煎后煮也算这个）。列表头写成 cook Method 也可以。</t>
+  </si>
+  <si>
+    <t>这种食材要几份</t>
+  </si>
+  <si>
+    <t>整数。空着、或填 0 和负数，都当成 1。</t>
+  </si>
+  <si>
+    <t>RecipeSeasonings</t>
+  </si>
+  <si>
+    <t>这道菜的调料加在哪份食材上，以及先后</t>
+  </si>
+  <si>
+    <t>一行是一次调味。同一道菜、同一份食材写多行时，从上到下就是加调料的顺序，判定按这个顺序。</t>
+  </si>
+  <si>
+    <t>先油后盐，都加在蘑菇上</t>
+  </si>
+  <si>
+    <t>哪种调料</t>
+  </si>
+  <si>
+    <t>填 Seasonings 的 id。列表头写成 seasoning Id 也可以。</t>
+  </si>
+  <si>
+    <t>加到哪份食材上</t>
+  </si>
+  <si>
+    <t>填 Ingredients 的 id，而且这道菜的 RecipeIngredients 里要有它。列表头写成 target Ingredient Id 也可以。</t>
+  </si>
+  <si>
+    <t>这一次加几份</t>
+  </si>
+  <si>
+    <t>整数。空着、或填 0 和负数，都当成 1。现在玩法里倒一次就是加上这个调料，不扣瓶子的数量。</t>
+  </si>
+  <si>
+    <t>RecipeSteps</t>
+  </si>
+  <si>
+    <t>可以没有</t>
+  </si>
+  <si>
+    <t>做菜步骤的备忘文字</t>
+  </si>
+  <si>
+    <t>可以整张不放。放了会写进食谱资产，但现在不算分，也不进日记。日记正文在 DiaryTables.xlsx。</t>
+  </si>
+  <si>
+    <t>有这行就必填</t>
+  </si>
+  <si>
+    <t>步骤序号</t>
+  </si>
+  <si>
+    <t>整数。导入后按这个数字从小到大排，不一定靠行在表里的上下位置。</t>
+  </si>
+  <si>
+    <t>这一步给人看的句子</t>
+  </si>
+  <si>
+    <t>中文短句。</t>
+  </si>
+  <si>
+    <t>这一步在做什么</t>
+  </si>
+  <si>
+    <t>Cut 切，Boil 煮，Fry 煎，Season 调味，Plate 装盘。空着当成 Cut。</t>
+  </si>
+  <si>
+    <t>这一步主要碰到的食材</t>
+  </si>
+  <si>
+    <t>填 Ingredients 的 id。没有就空着。</t>
+  </si>
+  <si>
+    <t>这一步结束时的烹饪方法</t>
+  </si>
+  <si>
+    <t>Raw / Boiled / Fried / BoiledAndFried。空着当成 Raw。</t>
+  </si>
+  <si>
+    <t>这一步用到的调料</t>
+  </si>
+  <si>
+    <t>填 Seasonings 的 id。没有就空着。</t>
+  </si>
+  <si>
+    <t>Ingredients</t>
+  </si>
+  <si>
+    <t>一种食材的固定资料</t>
+  </si>
+  <si>
+    <t>熟度、形状、有没有煎过，是玩的时候变的，不写在这张表。这里写这种食材永远不变的规则和介绍。</t>
+  </si>
+  <si>
+    <t>食材 id</t>
+  </si>
+  <si>
+    <t>ing_ 加英文。采集、背包、食谱都用它。定了不要改。</t>
+  </si>
+  <si>
+    <t>中文名</t>
+  </si>
+  <si>
+    <t>材料栏悬停详情的第一行，直接显示这个名字，前面不加属性名。</t>
+  </si>
+  <si>
+    <t>displayNameEn</t>
+  </si>
+  <si>
+    <t>英文名</t>
+  </si>
+  <si>
+    <t>语言切到英文时，详情第一行用它。空着就仍显示中文名。</t>
+  </si>
+  <si>
+    <t>中文介绍</t>
+  </si>
+  <si>
+    <t>悬停详情里，食物描述下面的正文。</t>
+  </si>
+  <si>
+    <t>descriptionEn</t>
+  </si>
+  <si>
+    <t>英文介绍</t>
+  </si>
+  <si>
+    <t>语言切到英文时的正文。空着就仍显示中文介绍。英文不显示「食物描述：」这几个字。</t>
+  </si>
+  <si>
+    <t>A fungus that grows in the forest...</t>
+  </si>
+  <si>
+    <t>类别</t>
+  </si>
+  <si>
+    <t>Meat 肉，Vegetable 蔬菜，Other 其他。评分用来区分荤素。悬停时显示的中文在 AttributeNames，对得上 kind.Meat、kind.Vegetable、kind.Other。</t>
+  </si>
+  <si>
+    <t>能不能生着吃</t>
+  </si>
+  <si>
+    <t>1 能生吃。0 生着吃会吃亏，要煮到一定熟度。悬停句子不显示 true/false：1 显示 AttributeNames 里 canEatRaw.true 的字（现在是可煎煮），0 显示 canEatRaw.false（现在是不可煎煮）。要改说法，改那两行，不要改这里的 1 和 0 的含义。</t>
+  </si>
+  <si>
+    <t>能不能切</t>
+  </si>
+  <si>
+    <t>1 可以拖上砧板切。0 拖上去会回到背包。悬停：1 显示 canCut.true（现在是可切），0 显示 canCut.false（现在是不可切）。</t>
+  </si>
+  <si>
+    <t>最佳熟度</t>
+  </si>
+  <si>
+    <t>数字，可以有小数。悬停显示这个数。评分时，当前熟度离它不超过 10 会加分。</t>
+  </si>
+  <si>
+    <t>最大熟度</t>
+  </si>
+  <si>
+    <t>数字。开火之后熟度不会超过它。悬停显示这个数。</t>
+  </si>
+  <si>
+    <t>整块时的默认图</t>
+  </si>
+  <si>
+    <t>图片路径。也可以叫 spriteWholePath。空着不会清掉已经导入的图。某种切法或煮法要换图，写到 IngredientVisualStates。</t>
+  </si>
+  <si>
+    <t>Assets/_Project/Arts/Ingrediant/....png</t>
+  </si>
+  <si>
+    <t>底色</t>
+  </si>
+  <si>
+    <t>写 #FFFFFF，或用逗号分开的 r,g,b，也可以再加透明度 r,g,b,a。空着不动原来的颜色。</t>
+  </si>
+  <si>
+    <t>IngredientVisualStates</t>
+  </si>
+  <si>
+    <t>同一种食材在不同形状、不同煮法下换哪张图</t>
+  </si>
+  <si>
+    <t>一行是一种样子。同一种食材把要的样子都写上。导入后，这种食材只保留表里这些行，表里没写的旧样子会被换掉。完全没出现在这张表里的食材，原来的图保持不动。</t>
+  </si>
+  <si>
+    <t>整朵生蘑菇一张图，切片再生一张图</t>
+  </si>
+  <si>
+    <t>填 Ingredients 的 id。</t>
+  </si>
+  <si>
+    <t>形状</t>
+  </si>
+  <si>
+    <t>Whole / Dice / Slice / Shred。</t>
+  </si>
+  <si>
+    <t>烹饪方法</t>
+  </si>
+  <si>
+    <t>Raw / Boiled / Fried / BoiledAndFried。</t>
+  </si>
+  <si>
+    <t>这一样子用的图</t>
+  </si>
+  <si>
+    <t>图片路径。也可以叫 spritePath。空着表示这个样子没有专门的图。</t>
+  </si>
+  <si>
+    <t>AttributeNames</t>
+  </si>
+  <si>
+    <t>悬停详情里的固定用词，中英各一列</t>
+  </si>
+  <si>
+    <t>食材名字、介绍、最佳熟度、最大熟度的数字不写在这里，它们来自 Ingredients。这里只写每一种食材都共用的属性名和选项。下面列出的 id 一个都不能少、不能改名，改文案只改 textZh 和 textEn。</t>
+  </si>
+  <si>
+    <t>类别： / Kind:</t>
+  </si>
+  <si>
+    <t>这条用词的编号</t>
+  </si>
+  <si>
+    <t>必须和下面清单里的字完全一致。多写别的 id 可以留下，但清单里的不能删。</t>
+  </si>
+  <si>
+    <t>中文</t>
+  </si>
+  <si>
+    <t>语言是中文时用这格。允许空：空表示中文界面不显示这几个字。这一列不会删掉你故意留下的空格。</t>
+  </si>
+  <si>
+    <t>英文</t>
+  </si>
+  <si>
+    <t>语言是英文时用这格。允许空。state.joiner 的英文要保留分号后面的空格。</t>
+  </si>
+  <si>
+    <t>id不能改</t>
+  </si>
+  <si>
+    <t>食物描述前面的几个字</t>
+  </si>
+  <si>
+    <t>中文现在是「食物描述：」。英文留空，英文界面只显示介绍正文，不显示 Description。</t>
+  </si>
+  <si>
+    <t>类别前面的属性名</t>
+  </si>
+  <si>
+    <t>中文「类别：」，英文「Kind:」。后面的蔬菜、肉、其他由 kind.Vegetable 那几行决定。</t>
+  </si>
+  <si>
+    <t>最佳熟度前面的属性名</t>
+  </si>
+  <si>
+    <t>中文「最佳熟度：」，英文「OptimalDoneness:」。数字来自食材的 optimalDoneness。</t>
+  </si>
+  <si>
+    <t>最佳熟度： / OptimalDoneness:</t>
+  </si>
+  <si>
+    <t>最大熟度前面的属性名</t>
+  </si>
+  <si>
+    <t>中文「最大熟度：」，英文「MaxDoneness:」。数字来自食材的 maxDoneness。</t>
+  </si>
+  <si>
+    <t>最大熟度： / MaxDoneness:</t>
+  </si>
+  <si>
+    <t>状态前面的属性名</t>
+  </si>
+  <si>
+    <t>中文「状态：」，英文「State:」。后面的内容是形状用词、连接符、烹饪方法用词拼起来，例如「整块；生的」。</t>
+  </si>
+  <si>
+    <t>状态： / State:</t>
+  </si>
+  <si>
+    <t>能否生吃在英文里的属性名</t>
+  </si>
+  <si>
+    <t>中文留空，中文直接显示可煎煮或不可煎煮，不再加一个标题。英文填 CanEatRaw:，界面会变成 CanEatRaw: True 这种。</t>
+  </si>
+  <si>
+    <t>能否切在英文里的属性名</t>
+  </si>
+  <si>
+    <t>中文留空。英文填 CanCut:。</t>
+  </si>
+  <si>
+    <t>canEatRaw 填了 1 时显示的句子</t>
+  </si>
+  <si>
+    <t>中文现在是可煎煮。英文 True 会接在 CanEatRaw: 后面。</t>
+  </si>
+  <si>
+    <t>可煎煮 / True</t>
+  </si>
+  <si>
+    <t>canEatRaw 填了 0 时显示的句子</t>
+  </si>
+  <si>
+    <t>中文现在是不可煎煮。白蘑菇是 0，所以悬停是不可煎煮。</t>
+  </si>
+  <si>
+    <t>不可煎煮 / False</t>
+  </si>
+  <si>
+    <t>canCut 填了 1 时显示的句子</t>
+  </si>
+  <si>
+    <t>中文现在是可切。</t>
+  </si>
+  <si>
+    <t>可切 / True</t>
+  </si>
+  <si>
+    <t>canCut 填了 0 时显示的句子</t>
+  </si>
+  <si>
+    <t>中文现在是不可切。</t>
+  </si>
+  <si>
+    <t>不可切 / False</t>
+  </si>
+  <si>
+    <t>kind 填 Meat 时显示的类别</t>
+  </si>
+  <si>
+    <t>中文肉类，英文 Meat。</t>
+  </si>
+  <si>
+    <t>肉类 / Meat</t>
+  </si>
+  <si>
+    <t>kind 填 Vegetable 时显示的类别</t>
+  </si>
+  <si>
+    <t>中文蔬菜，英文 Vegetable。</t>
+  </si>
+  <si>
+    <t>蔬菜 / Vegetable</t>
+  </si>
+  <si>
+    <t>kind 填 Other 时显示的类别</t>
+  </si>
+  <si>
+    <t>中文其他，英文 Other。</t>
+  </si>
+  <si>
+    <t>其他 / Other</t>
+  </si>
+  <si>
+    <t>形状：整块</t>
+  </si>
+  <si>
+    <t>状态后半用。中文整块，英文 Whole。</t>
+  </si>
+  <si>
+    <t>整块 / Whole</t>
+  </si>
+  <si>
+    <t>形状：切丁</t>
+  </si>
+  <si>
+    <t>中文切丁状，英文 Dice。</t>
+  </si>
+  <si>
+    <t>切丁状 / Dice</t>
+  </si>
+  <si>
+    <t>形状：切片</t>
+  </si>
+  <si>
+    <t>中文片状，英文 Slice。</t>
+  </si>
+  <si>
+    <t>片状 / Slice</t>
+  </si>
+  <si>
+    <t>形状：切丝</t>
+  </si>
+  <si>
+    <t>中文丝状，英文 Shred。</t>
+  </si>
+  <si>
+    <t>丝状 / Shred</t>
+  </si>
+  <si>
+    <t>烹饪方法：生的</t>
+  </si>
+  <si>
+    <t>中文生的，英文 Raw。</t>
+  </si>
+  <si>
+    <t>生的 / Raw</t>
+  </si>
+  <si>
+    <t>烹饪方法：煮过</t>
+  </si>
+  <si>
+    <t>中文煮过，英文 Boiled。</t>
+  </si>
+  <si>
+    <t>煮过 / Boiled</t>
+  </si>
+  <si>
+    <t>烹饪方法：煎过</t>
+  </si>
+  <si>
+    <t>中文煎过，英文 Fried。</t>
+  </si>
+  <si>
+    <t>煎过 / Fried</t>
+  </si>
+  <si>
+    <t>烹饪方法：煎煮过</t>
+  </si>
+  <si>
+    <t>中文煎煮过，英文 BoiledAndFried。</t>
+  </si>
+  <si>
+    <t>煎煮过 / BoiledAndFried</t>
+  </si>
+  <si>
+    <t>状态里形状和烹饪方法中间的符号</t>
+  </si>
+  <si>
+    <t>中文用全角分号「；」，后面不要加空格。英文用半角分号再加一个空格，写成「; 」里分号后的那一格空格要留着。拼出来是「整块；生的」和「Whole; Raw」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">；  /  ; </t>
+  </si>
+  <si>
+    <t>每张表、每一列怎么填，看第一张「备忘」。备忘本身不导入。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -906,8 +1603,17 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -917,6 +1623,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D6C4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -932,13 +1644,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1241,7 +1957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -1287,6 +2003,154 @@
         <v>259</v>
       </c>
     </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="58.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>176</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1294,6 +2158,1719 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C33CE7-322A-4AFA-A131-610257608A26}">
+  <sheetPr>
+    <tabColor rgb="FF47AD70"/>
+  </sheetPr>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.6328125" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="42.6328125" customWidth="1"/>
+    <col min="5" max="5" width="62.6328125" customWidth="1"/>
+    <col min="6" max="6" width="40.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F32" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="56" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="F48" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="F49" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="F50" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="F51" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{C2C33CE7-322A-4AFA-A131-610257608A26}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -1368,7 +3945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -1518,7 +4095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -1859,7 +4436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -2338,7 +4915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -2897,7 +5474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -3481,7 +6058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817F8083-EF7C-49A5-9492-A26103C87A7B}">
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -3749,147 +6326,4 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="58.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>176</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
+++ b/CookingClient/Assets/_Project/Data/Tables/CookingTables.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\TGJ_music\CookingClient\Assets\_Project\Data\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9818EC25-8ABC-4919-A606-567B5A4B8C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15FF6BB-977A-4373-A846-D81119889678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1210" windowWidth="18420" windowHeight="13270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1210" windowWidth="18420" windowHeight="13270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="说明" sheetId="1" r:id="rId1"/>
-    <sheet name="备忘" sheetId="10" r:id="rId2"/>
+    <sheet name="备忘" sheetId="11" r:id="rId1"/>
+    <sheet name="说明" sheetId="1" r:id="rId2"/>
     <sheet name="Seasonings" sheetId="2" r:id="rId3"/>
     <sheet name="Recipes" sheetId="3" r:id="rId4"/>
     <sheet name="RecipeIngredients" sheetId="4" r:id="rId5"/>
@@ -25,7 +25,7 @@
     <sheet name="IngredientVisualStates" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">备忘!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">备忘!$A$1:$F$85</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -1553,14 +1553,15 @@
     <t xml:space="preserve">；  /  ; </t>
   </si>
   <si>
-    <t>每张表、每一列怎么填，看第一张「备忘」。备忘本身不导入。</t>
+    <t>每一列的含义和填法在最前面的「备忘」。备忘和说明都不导入。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1607,13 +1608,19 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1627,7 +1634,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA0D6C4"/>
+        <fgColor rgb="FFB0D6C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E6F3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1644,15 +1657,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1956,61 +1974,1715 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F27D4C3B-CD06-45CF-B2DE-CFFD0AFC6E0C}">
+  <sheetPr>
+    <tabColor indexed="13"/>
+  </sheetPr>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="72" customWidth="1"/>
+    <col min="1" max="1" width="26.6328125" customWidth="1"/>
+    <col min="2" max="2" width="24.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="36.6328125" customWidth="1"/>
+    <col min="5" max="5" width="62.6328125" customWidth="1"/>
+    <col min="6" max="6" width="42.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="F18" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F27" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="F32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="F35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="F48" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>495</v>
+    <row r="49" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="F49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="F50" s="8">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="F51" s="8">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A66" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A67" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A68" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F85" xr:uid="{F27D4C3B-CD06-45CF-B2DE-CFFD0AFC6E0C}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2158,1715 +3830,61 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C33CE7-322A-4AFA-A131-610257608A26}">
-  <sheetPr>
-    <tabColor rgb="FF47AD70"/>
-  </sheetPr>
-  <dimension ref="A1:F85"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.6328125" customWidth="1"/>
-    <col min="2" max="2" width="28.6328125" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="4" max="4" width="42.6328125" customWidth="1"/>
-    <col min="5" max="5" width="62.6328125" customWidth="1"/>
-    <col min="6" max="6" width="40.6328125" customWidth="1"/>
+    <col min="1" max="1" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="F18" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="F27" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F32" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="F35" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="56" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="F48" s="7">
+    <row r="1" spans="1:1" ht="17.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="F49" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="F50" s="7">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="F51" s="7">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>494</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>495</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{C2C33CE7-322A-4AFA-A131-610257608A26}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
